--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-18T09:24:58+00:00</t>
+    <t>2025-02-07T10:03:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:03:43+00:00</t>
+    <t>2025-02-07T10:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:49:13+00:00</t>
+    <t>2025-02-07T11:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,7 +502,7 @@
     <t>Slot.serviceType</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableReference(HealthcareService)
+    <t xml:space="preserve">CodeableReference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice)
 </t>
   </si>
   <si>
@@ -512,7 +512,10 @@
     <t>The type of appointments that can be booked into this slot (ideally this would be an identifiable service - which is at a location, rather than the location itself). If provided then this overrides the value provided on the Schedule resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>Slot.specialty</t>
@@ -551,7 +554,7 @@
     <t>Slot.schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Schedule)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-schedule)
 </t>
   </si>
   <si>
@@ -943,7 +946,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="37.2578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="111.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -958,7 +961,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.81640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.80859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.62890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -2366,11 +2369,11 @@
         <v>18</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>18</v>
@@ -2414,10 +2417,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2443,10 +2446,10 @@
         <v>149</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2473,13 +2476,13 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -2497,7 +2500,7 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2523,10 +2526,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2552,13 +2555,13 @@
         <v>149</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2584,11 +2587,11 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -2606,7 +2609,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2632,10 +2635,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2658,13 +2661,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2715,7 +2718,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>84</v>
@@ -2741,10 +2744,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2770,10 +2773,10 @@
         <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2803,10 +2806,10 @@
         <v>108</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
@@ -2824,7 +2827,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>84</v>
@@ -2845,15 +2848,15 @@
         <v>18</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2876,13 +2879,13 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2933,7 +2936,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -2948,21 +2951,21 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2985,13 +2988,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3042,7 +3045,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3057,21 +3060,21 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3094,13 +3097,13 @@
         <v>18</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3108,7 +3111,7 @@
         <v>18</v>
       </c>
       <c r="Q20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R20" t="s" s="2">
         <v>18</v>
@@ -3153,7 +3156,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3179,10 +3182,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3205,13 +3208,13 @@
         <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3262,7 +3265,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T11:56:07+00:00</t>
+    <t>2025-03-08T15:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T15:01:54+00:00</t>
+    <t>2025-03-08T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T16:16:40+00:00</t>
+    <t>2025-03-12T07:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T07:45:08+00:00</t>
+    <t>2025-03-21T10:14:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T13:03:45+00:00</t>
+    <t>2026-01-12T10:11:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:11:28+00:00</t>
+    <t>2026-01-12T10:18:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:18:34+00:00</t>
+    <t>2026-01-12T10:26:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:26:55+00:00</t>
+    <t>2026-01-28T07:37:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:37:37+00:00</t>
+    <t>2026-01-28T07:43:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:43:18+00:00</t>
+    <t>2026-01-28T07:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:44:30+00:00</t>
+    <t>2026-01-28T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:46:49+00:00</t>
+    <t>2026-02-24T18:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T18:21:42+00:00</t>
+    <t>2026-02-26T08:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:55:53+00:00</t>
+    <t>2026-03-06T07:38:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T07:38:40+00:00</t>
+    <t>2026-03-06T14:26:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="218">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:26:35+00:00</t>
+    <t>2026-03-09T09:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -475,6 +475,22 @@
   </si>
   <si>
     <t>An optional URL that can be used for redirects to a webpage for booking an Appointment. It should contain identifying information about the Slot so that it can be preselected on the target booking page.</t>
+  </si>
+  <si>
+    <t>Slot.extension:cancellationPolicy</t>
+  </si>
+  <si>
+    <t>cancellationPolicy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
+</t>
+  </si>
+  <si>
+    <t>The policy for a cancellation</t>
+  </si>
+  <si>
+    <t>This Extension provides the information about the policy of a cancellation of an appointment. It can contain a time frame until when a cancellation is possible or what the fee for a cancellation will be.</t>
   </si>
   <si>
     <t>Slot.modifierExtension</t>
@@ -972,7 +988,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:AM24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="27.8125" customWidth="true" bestFit="true"/>
@@ -2241,43 +2257,41 @@
         <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>153</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>18</v>
       </c>
@@ -2325,7 +2339,7 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2343,7 +2357,7 @@
         <v>18</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>18</v>
@@ -2351,14 +2365,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2371,22 +2385,26 @@
         <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>18</v>
       </c>
@@ -2434,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2446,13 +2464,13 @@
         <v>18</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>18</v>
@@ -2519,11 +2537,13 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -2556,7 +2576,7 @@
         <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>18</v>
@@ -2567,10 +2587,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2593,13 +2613,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2626,11 +2646,11 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -2648,7 +2668,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2663,7 +2683,7 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>18</v>
@@ -2674,10 +2694,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2700,7 +2720,7 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>174</v>
@@ -2735,12 +2755,10 @@
       <c r="X16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
       </c>
@@ -2757,7 +2775,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -2772,7 +2790,7 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>18</v>
@@ -2783,10 +2801,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2809,17 +2827,15 @@
         <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>182</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -2844,9 +2860,11 @@
         <v>18</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="Z17" t="s" s="2">
         <v>183</v>
       </c>
@@ -2866,7 +2884,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2881,7 +2899,7 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>18</v>
@@ -2903,10 +2921,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>18</v>
@@ -2918,15 +2936,17 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -2951,13 +2971,11 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -2978,10 +2996,10 @@
         <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>18</v>
@@ -2990,7 +3008,7 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>18</v>
@@ -3001,10 +3019,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3027,13 +3045,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3060,13 +3078,13 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>18</v>
@@ -3084,7 +3102,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3105,15 +3123,15 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3136,13 +3154,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3169,13 +3187,13 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -3193,7 +3211,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3208,21 +3226,21 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3245,7 +3263,7 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>201</v>
@@ -3302,7 +3320,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>84</v>
@@ -3317,21 +3335,21 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3339,7 +3357,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>84</v>
@@ -3351,10 +3369,10 @@
         <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>206</v>
@@ -3367,9 +3385,7 @@
       <c r="P22" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q22" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
         <v>18</v>
       </c>
@@ -3413,10 +3429,10 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>84</v>
@@ -3428,13 +3444,13 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>18</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23">
@@ -3478,7 +3494,9 @@
       <c r="P23" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="Q23" s="2"/>
+      <c r="Q23" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="R23" t="s" s="2">
         <v>18</v>
       </c>
@@ -3543,6 +3561,115 @@
         <v>18</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>18</v>
       </c>
     </row>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T09:58:26+00:00</t>
+    <t>2026-03-11T09:54:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T09:54:15+00:00</t>
+    <t>2026-03-18T07:58:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T07:58:35+00:00</t>
+    <t>2026-04-07T11:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:55:37+00:00</t>
+    <t>2026-04-08T07:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T07:58:25+00:00</t>
+    <t>2026-06-09T13:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:05:25+00:00</t>
+    <t>2026-06-09T13:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:44:21+00:00</t>
+    <t>2026-06-09T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T19:55:01+00:00</t>
+    <t>2026-06-10T09:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-slot</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-slot</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:07:46+00:00</t>
+    <t>2026-08-18T08:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -451,7 +451,7 @@
     <t>SlotEncounterClass</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/slot-encounter-class}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/slot-encounter-class}
 </t>
   </si>
   <si>
@@ -467,7 +467,7 @@
     <t>bookingURL</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/appointment-booking-url}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/appointment-booking-url}
 </t>
   </si>
   <si>
@@ -483,7 +483,7 @@
     <t>cancellationPolicy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
 </t>
   </si>
   <si>
@@ -557,7 +557,7 @@
     <t>Slot.serviceType</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableReference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice)
+    <t xml:space="preserve">CodeableReference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-healthcareservice)
 </t>
   </si>
   <si>
@@ -570,7 +570,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>Slot.specialty</t>
@@ -609,7 +609,7 @@
     <t>Slot.schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-schedule)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-schedule)
 </t>
   </si>
   <si>
@@ -1001,7 +1001,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.4921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="88.125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1016,7 +1016,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.28515625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.6953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:43:24+00:00</t>
+    <t>2026-08-18T13:20:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:20:27+00:00</t>
+    <t>2026-08-31T14:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-slot.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:45:12+00:00</t>
+    <t>2026-09-01T07:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
